--- a/financial_models/output/Azalea_Hospice_SBA_Loan_Package.xlsx
+++ b/financial_models/output/Azalea_Hospice_SBA_Loan_Package.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sources &amp; Uses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Lender Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Stress Tests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Revenue Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Staffing &amp; Payroll" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Operating Budget" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Detailed P&amp;L" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Debt Schedule" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cash Flow &amp; BS" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Actuals vs Model" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Uses" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lender Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="rhc_tier1">Inputs!$B$5</definedName>
@@ -1209,7 +1209,7 @@
     </comment>
     <comment ref="B110" authorId="0" shapeId="0">
       <text>
-        <t>Sized to fund ramp-period operating need + startup costs. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Sized to pay the seller in full at close + fund startup costs and working-capital reserve. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0" shapeId="0">
@@ -1224,7 +1224,7 @@
     </comment>
     <comment ref="B113" authorId="0" shapeId="0">
       <text>
-        <t>FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Cash capital contribution by James Bullard (19.5% passive member). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B114" authorId="0" shapeId="0">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="B110" s="9" t="n">
-        <v>500000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="111">
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="B113" s="9" t="n">
-        <v>250000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="114">
@@ -3636,11 +3636,11 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>Opening cash = equity + loan - startup - capex</t>
+          <t>Opening cash = equity + loan - startup - capex - license (paid at close)</t>
         </is>
       </c>
       <c r="B139" s="23">
-        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117</f>
+        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117-Inputs!$B$120</f>
         <v/>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="B34" s="25">
-        <f>Inputs!$B$120</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="C34" s="25">
@@ -6941,7 +6941,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sources &amp; Uses of Financing - Hickory CHOW acquisition + working capital | SBA + seller note + equity</t>
+          <t>Sources &amp; Uses of Financing - Hickory CHOW (seller paid at close) + working capital | SBA + equity</t>
         </is>
       </c>
     </row>
@@ -6980,11 +6980,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Hickory license seller note</t>
+          <t>Owner equity injection</t>
         </is>
       </c>
       <c r="B6" s="25">
-        <f>Inputs!$B$120</f>
+        <f>Inputs!$B$113</f>
         <v/>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -6998,13 +6998,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Owner equity injection</t>
-        </is>
-      </c>
-      <c r="B7" s="25">
-        <f>Inputs!$B$113</f>
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL SOURCES</t>
+        </is>
+      </c>
+      <c r="B7" s="27">
+        <f>SUM(B5:B6)</f>
         <v/>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -7018,15 +7018,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL SOURCES</t>
-        </is>
-      </c>
-      <c r="B8" s="27">
-        <f>SUM(B5:B7)</f>
-        <v/>
-      </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>EMR implementation / setup</t>
@@ -7110,14 +7101,14 @@
         </is>
       </c>
       <c r="B16" s="28">
-        <f>B8-D14</f>
+        <f>B7-D14</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>CHOW acquisition: Azalea acquires Hickory Hospice's existing Medicare-certified provider number ($300K, 36 months at 6% seller-financed) - gives Azalea immediate billing capability in San Antonio and an alternative-delivery site serving the East Texas / Tyler market. CHAP/ACHC accreditation transfers with the CHOW; 855A change-of-ownership preserves the provider number with no fresh enrollment delay. The seller note self-finances the license - it shows on both sides above.</t>
+          <t>CHOW acquisition: Azalea acquires Hickory Hospice's existing Medicare-certified provider number ($300K, paid in full at close from SBA loan + equity proceeds) - gives Azalea immediate billing capability in San Antonio and an alternative-delivery site serving the East Texas / Tyler market. CHAP/ACHC accreditation transfers with the CHOW; 855A change-of-ownership preserves the provider number with no fresh enrollment delay. With no seller note, the SBA loan is the only debt the business carries.</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7153,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lender Summary - COMBINED debt-service coverage (SBA + Hickory seller note) vs SBA floor 1.25x</t>
+          <t>Lender Summary - SBA 7(a) debt-service coverage (seller paid at close) vs SBA floor 1.25x</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7361,7 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Azalea acquires Hickory Hospice's already-certified Medicare provider number via a $300K CHOW (seller-financed at 6% over 36 months), eliminating the 855A enrollment cash gap a fresh startup would face - Azalea bills from day 1 in San Antonio and operates an alternative-delivery site for Tyler/East Texas. The migrated Paloma clinical team brings a proven ~$118K/mo, ~22 ADC book of business. Coverage shown here is COMBINED (SBA + seller note); the seller note retires at month 36, after which DSCR jumps as only the SBA service remains.</t>
+          <t>Azalea acquires Hickory Hospice's already-certified Medicare provider number via a $300K CHOW (paid in full at close), eliminating the 855A enrollment cash gap a fresh startup would face - Azalea bills from day 1 in San Antonio and operates an alternative-delivery site for Tyler/East Texas. The migrated Paloma clinical team brings a proven ~$118K/mo, ~22 ADC book of business. With the seller paid at close, the SBA loan is the only debt the business carries, so the coverage shown here is SBA-only - strong from Year 1.</t>
         </is>
       </c>
     </row>
@@ -18448,7 +18439,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Debt Schedule - SBA 7(a) + Hickory license seller note | Combined DSCR shown (target &gt;= 1.25x)</t>
+          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
         </is>
       </c>
     </row>
@@ -18477,7 +18468,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>PMT(Inputs!$B$121/12,Inputs!$B$122,-Inputs!$B$120)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -19051,7 +19042,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HICKORY LICENSE SELLER NOTE ($300K, 6%, 36 mo)</t>
+          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
         </is>
       </c>
     </row>
@@ -19062,7 +19053,7 @@
         </is>
       </c>
       <c r="C18" s="25">
-        <f>Inputs!$B$120</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="D18" s="24">
@@ -19493,7 +19484,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>COMBINED DEBT SERVICE &amp; COVERAGE</t>
+          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19665,7 @@
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>TOTAL DEBT SERVICE (P+I, combined)</t>
+          <t>TOTAL DEBT SERVICE (P+I)</t>
         </is>
       </c>
       <c r="C27" s="23">
@@ -19848,7 +19839,7 @@
     <row r="29">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>COMBINED DSCR (period)</t>
+          <t>DSCR (period)</t>
         </is>
       </c>
       <c r="C29" s="57">

--- a/financial_models/output/Azalea_Hospice_SBA_Loan_Package.xlsx
+++ b/financial_models/output/Azalea_Hospice_SBA_Loan_Package.xlsx
@@ -11,13 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Uses" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lender Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVI Upside" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="rhc_tier1">Inputs!$B$5</definedName>
@@ -388,6 +389,9 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -405,9 +409,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1349,6 +1350,21 @@
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
+        <t>Sustained incremental census from MVI 'Perfect Visit' certification + the national campaign. Illustrative only - not used for underwriting.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Azalea Hospice</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
         <t>Source: Paloma P&amp;L 2025.</t>
       </text>
     </comment>
@@ -3688,6 +3704,1550 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AZALEA HOSPICE &amp; PALLIATIVE CARE - Tyler, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>LOAN TERMS (from Inputs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SBA monthly payment (PMT)</t>
+        </is>
+      </c>
+      <c r="B5" s="24">
+        <f>PMT(Inputs!$B$111/12,Inputs!$B$112,-Inputs!$B$110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>License note monthly payment (PMT)</t>
+        </is>
+      </c>
+      <c r="B6" s="24">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>($ per period)</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>YEAR 1 - monthly</t>
+        </is>
+      </c>
+      <c r="O8" s="42" t="inlineStr">
+        <is>
+          <t>YEAR 2 - quarterly</t>
+        </is>
+      </c>
+      <c r="S8" s="42" t="inlineStr">
+        <is>
+          <t>YEAR 3 - quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="J9" s="30" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="K9" s="30" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="L9" s="30" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="M9" s="30" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="N9" s="30" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="O9" s="30" t="inlineStr">
+        <is>
+          <t>Y2 Q1</t>
+        </is>
+      </c>
+      <c r="P9" s="30" t="inlineStr">
+        <is>
+          <t>Y2 Q2</t>
+        </is>
+      </c>
+      <c r="Q9" s="30" t="inlineStr">
+        <is>
+          <t>Y2 Q3</t>
+        </is>
+      </c>
+      <c r="R9" s="30" t="inlineStr">
+        <is>
+          <t>Y2 Q4</t>
+        </is>
+      </c>
+      <c r="S9" s="30" t="inlineStr">
+        <is>
+          <t>Y3 Q1</t>
+        </is>
+      </c>
+      <c r="T9" s="30" t="inlineStr">
+        <is>
+          <t>Y3 Q2</t>
+        </is>
+      </c>
+      <c r="U9" s="30" t="inlineStr">
+        <is>
+          <t>Y3 Q3</t>
+        </is>
+      </c>
+      <c r="V9" s="30" t="inlineStr">
+        <is>
+          <t>Y3 Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>SBA 7(a) LOAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Beginning balance</t>
+        </is>
+      </c>
+      <c r="C11" s="25">
+        <f>Inputs!$B$110</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>E15</f>
+        <v/>
+      </c>
+      <c r="G11" s="24">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="H11" s="24">
+        <f>G15</f>
+        <v/>
+      </c>
+      <c r="I11" s="24">
+        <f>H15</f>
+        <v/>
+      </c>
+      <c r="J11" s="24">
+        <f>I15</f>
+        <v/>
+      </c>
+      <c r="K11" s="24">
+        <f>J15</f>
+        <v/>
+      </c>
+      <c r="L11" s="24">
+        <f>K15</f>
+        <v/>
+      </c>
+      <c r="M11" s="24">
+        <f>L15</f>
+        <v/>
+      </c>
+      <c r="N11" s="24">
+        <f>M15</f>
+        <v/>
+      </c>
+      <c r="O11" s="24">
+        <f>N15</f>
+        <v/>
+      </c>
+      <c r="P11" s="24">
+        <f>O15</f>
+        <v/>
+      </c>
+      <c r="Q11" s="24">
+        <f>P15</f>
+        <v/>
+      </c>
+      <c r="R11" s="24">
+        <f>Q15</f>
+        <v/>
+      </c>
+      <c r="S11" s="24">
+        <f>R15</f>
+        <v/>
+      </c>
+      <c r="T11" s="24">
+        <f>S15</f>
+        <v/>
+      </c>
+      <c r="U11" s="24">
+        <f>T15</f>
+        <v/>
+      </c>
+      <c r="V11" s="24">
+        <f>U15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="C12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="H12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="I12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="J12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="K12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="L12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="M12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="N12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="O12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="P12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="Q12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="R12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="S12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="T12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="U12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="V12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C13" s="24">
+        <f>C11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>D11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>E11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="F13" s="24">
+        <f>F11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="G13" s="24">
+        <f>G11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="H13" s="24">
+        <f>H11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="I13" s="24">
+        <f>I11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="J13" s="24">
+        <f>J11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="K13" s="24">
+        <f>K11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="L13" s="24">
+        <f>L11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="M13" s="24">
+        <f>M11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="N13" s="24">
+        <f>N11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="O13" s="24">
+        <f>O11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="P13" s="24">
+        <f>P11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="Q13" s="24">
+        <f>Q11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="R13" s="24">
+        <f>R11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="S13" s="24">
+        <f>S11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="T13" s="24">
+        <f>T11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="U13" s="24">
+        <f>U11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="V13" s="24">
+        <f>V11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="C14" s="24">
+        <f>C12-C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>D12-D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>E12-E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>F12-F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="24">
+        <f>G12-G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="24">
+        <f>H12-H13</f>
+        <v/>
+      </c>
+      <c r="I14" s="24">
+        <f>I12-I13</f>
+        <v/>
+      </c>
+      <c r="J14" s="24">
+        <f>J12-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="24">
+        <f>K12-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="24">
+        <f>L12-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="24">
+        <f>M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="24">
+        <f>N12-N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="24">
+        <f>O12-O13</f>
+        <v/>
+      </c>
+      <c r="P14" s="24">
+        <f>P12-P13</f>
+        <v/>
+      </c>
+      <c r="Q14" s="24">
+        <f>Q12-Q13</f>
+        <v/>
+      </c>
+      <c r="R14" s="24">
+        <f>R12-R13</f>
+        <v/>
+      </c>
+      <c r="S14" s="24">
+        <f>S12-S13</f>
+        <v/>
+      </c>
+      <c r="T14" s="24">
+        <f>T12-T13</f>
+        <v/>
+      </c>
+      <c r="U14" s="24">
+        <f>U12-U13</f>
+        <v/>
+      </c>
+      <c r="V14" s="24">
+        <f>V12-V13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Ending balance</t>
+        </is>
+      </c>
+      <c r="C15" s="23">
+        <f>C11-C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="23">
+        <f>D11-D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="23">
+        <f>E11-E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="23">
+        <f>F11-F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="23">
+        <f>G11-G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="23">
+        <f>H11-H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="23">
+        <f>I11-I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="23">
+        <f>J11-J14</f>
+        <v/>
+      </c>
+      <c r="K15" s="23">
+        <f>K11-K14</f>
+        <v/>
+      </c>
+      <c r="L15" s="23">
+        <f>L11-L14</f>
+        <v/>
+      </c>
+      <c r="M15" s="23">
+        <f>M11-M14</f>
+        <v/>
+      </c>
+      <c r="N15" s="23">
+        <f>N11-N14</f>
+        <v/>
+      </c>
+      <c r="O15" s="23">
+        <f>O11-O14</f>
+        <v/>
+      </c>
+      <c r="P15" s="23">
+        <f>P11-P14</f>
+        <v/>
+      </c>
+      <c r="Q15" s="23">
+        <f>Q11-Q14</f>
+        <v/>
+      </c>
+      <c r="R15" s="23">
+        <f>R11-R14</f>
+        <v/>
+      </c>
+      <c r="S15" s="23">
+        <f>S11-S14</f>
+        <v/>
+      </c>
+      <c r="T15" s="23">
+        <f>T11-T14</f>
+        <v/>
+      </c>
+      <c r="U15" s="23">
+        <f>U11-U14</f>
+        <v/>
+      </c>
+      <c r="V15" s="23">
+        <f>V11-V14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Beginning balance</t>
+        </is>
+      </c>
+      <c r="C18" s="25">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="F18" s="24">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="G18" s="24">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="H18" s="24">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="I18" s="24">
+        <f>H22</f>
+        <v/>
+      </c>
+      <c r="J18" s="24">
+        <f>I22</f>
+        <v/>
+      </c>
+      <c r="K18" s="24">
+        <f>J22</f>
+        <v/>
+      </c>
+      <c r="L18" s="24">
+        <f>K22</f>
+        <v/>
+      </c>
+      <c r="M18" s="24">
+        <f>L22</f>
+        <v/>
+      </c>
+      <c r="N18" s="24">
+        <f>M22</f>
+        <v/>
+      </c>
+      <c r="O18" s="24">
+        <f>N22</f>
+        <v/>
+      </c>
+      <c r="P18" s="24">
+        <f>O22</f>
+        <v/>
+      </c>
+      <c r="Q18" s="24">
+        <f>P22</f>
+        <v/>
+      </c>
+      <c r="R18" s="24">
+        <f>Q22</f>
+        <v/>
+      </c>
+      <c r="S18" s="24">
+        <f>R22</f>
+        <v/>
+      </c>
+      <c r="T18" s="24">
+        <f>S22</f>
+        <v/>
+      </c>
+      <c r="U18" s="24">
+        <f>T22</f>
+        <v/>
+      </c>
+      <c r="V18" s="24">
+        <f>U22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Ending balance (closed-form)</t>
+        </is>
+      </c>
+      <c r="C19" s="24">
+        <f>MAX(0,C18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>MAX(0,D18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>MAX(0,E18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="F19" s="24">
+        <f>MAX(0,F18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="G19" s="24">
+        <f>MAX(0,G18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="H19" s="24">
+        <f>MAX(0,H18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="I19" s="24">
+        <f>MAX(0,I18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="J19" s="24">
+        <f>MAX(0,J18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="K19" s="24">
+        <f>MAX(0,K18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="L19" s="24">
+        <f>MAX(0,L18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="M19" s="24">
+        <f>MAX(0,M18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="N19" s="24">
+        <f>MAX(0,N18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="O19" s="24">
+        <f>MAX(0,O18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="P19" s="24">
+        <f>MAX(0,P18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="24">
+        <f>MAX(0,Q18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="R19" s="24">
+        <f>MAX(0,R18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="S19" s="24">
+        <f>MAX(0,S18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="T19" s="24">
+        <f>MAX(0,T18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="U19" s="24">
+        <f>MAX(0,U18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="V19" s="24">
+        <f>MAX(0,V18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="C20" s="24">
+        <f>C18-C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>D18-D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>E18-E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
+        <f>F18-F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="24">
+        <f>G18-G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="24">
+        <f>H18-H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="24">
+        <f>I18-I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="24">
+        <f>J18-J19</f>
+        <v/>
+      </c>
+      <c r="K20" s="24">
+        <f>K18-K19</f>
+        <v/>
+      </c>
+      <c r="L20" s="24">
+        <f>L18-L19</f>
+        <v/>
+      </c>
+      <c r="M20" s="24">
+        <f>M18-M19</f>
+        <v/>
+      </c>
+      <c r="N20" s="24">
+        <f>N18-N19</f>
+        <v/>
+      </c>
+      <c r="O20" s="24">
+        <f>O18-O19</f>
+        <v/>
+      </c>
+      <c r="P20" s="24">
+        <f>P18-P19</f>
+        <v/>
+      </c>
+      <c r="Q20" s="24">
+        <f>Q18-Q19</f>
+        <v/>
+      </c>
+      <c r="R20" s="24">
+        <f>R18-R19</f>
+        <v/>
+      </c>
+      <c r="S20" s="24">
+        <f>S18-S19</f>
+        <v/>
+      </c>
+      <c r="T20" s="24">
+        <f>T18-T19</f>
+        <v/>
+      </c>
+      <c r="U20" s="24">
+        <f>U18-U19</f>
+        <v/>
+      </c>
+      <c r="V20" s="24">
+        <f>V18-V19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C21" s="24">
+        <f>MAX(0,IF(C18=0,0,'Debt Schedule'!$B$6*1-C20))</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>MAX(0,IF(D18=0,0,'Debt Schedule'!$B$6*1-D20))</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>MAX(0,IF(E18=0,0,'Debt Schedule'!$B$6*1-E20))</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>MAX(0,IF(F18=0,0,'Debt Schedule'!$B$6*1-F20))</f>
+        <v/>
+      </c>
+      <c r="G21" s="24">
+        <f>MAX(0,IF(G18=0,0,'Debt Schedule'!$B$6*1-G20))</f>
+        <v/>
+      </c>
+      <c r="H21" s="24">
+        <f>MAX(0,IF(H18=0,0,'Debt Schedule'!$B$6*1-H20))</f>
+        <v/>
+      </c>
+      <c r="I21" s="24">
+        <f>MAX(0,IF(I18=0,0,'Debt Schedule'!$B$6*1-I20))</f>
+        <v/>
+      </c>
+      <c r="J21" s="24">
+        <f>MAX(0,IF(J18=0,0,'Debt Schedule'!$B$6*1-J20))</f>
+        <v/>
+      </c>
+      <c r="K21" s="24">
+        <f>MAX(0,IF(K18=0,0,'Debt Schedule'!$B$6*1-K20))</f>
+        <v/>
+      </c>
+      <c r="L21" s="24">
+        <f>MAX(0,IF(L18=0,0,'Debt Schedule'!$B$6*1-L20))</f>
+        <v/>
+      </c>
+      <c r="M21" s="24">
+        <f>MAX(0,IF(M18=0,0,'Debt Schedule'!$B$6*1-M20))</f>
+        <v/>
+      </c>
+      <c r="N21" s="24">
+        <f>MAX(0,IF(N18=0,0,'Debt Schedule'!$B$6*1-N20))</f>
+        <v/>
+      </c>
+      <c r="O21" s="24">
+        <f>MAX(0,IF(O18=0,0,'Debt Schedule'!$B$6*3-O20))</f>
+        <v/>
+      </c>
+      <c r="P21" s="24">
+        <f>MAX(0,IF(P18=0,0,'Debt Schedule'!$B$6*3-P20))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="24">
+        <f>MAX(0,IF(Q18=0,0,'Debt Schedule'!$B$6*3-Q20))</f>
+        <v/>
+      </c>
+      <c r="R21" s="24">
+        <f>MAX(0,IF(R18=0,0,'Debt Schedule'!$B$6*3-R20))</f>
+        <v/>
+      </c>
+      <c r="S21" s="24">
+        <f>MAX(0,IF(S18=0,0,'Debt Schedule'!$B$6*3-S20))</f>
+        <v/>
+      </c>
+      <c r="T21" s="24">
+        <f>MAX(0,IF(T18=0,0,'Debt Schedule'!$B$6*3-T20))</f>
+        <v/>
+      </c>
+      <c r="U21" s="24">
+        <f>MAX(0,IF(U18=0,0,'Debt Schedule'!$B$6*3-U20))</f>
+        <v/>
+      </c>
+      <c r="V21" s="24">
+        <f>MAX(0,IF(V18=0,0,'Debt Schedule'!$B$6*3-V20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Ending balance</t>
+        </is>
+      </c>
+      <c r="C22" s="23">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="D22" s="23">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="E22" s="23">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F22" s="23">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G22" s="23">
+        <f>G19</f>
+        <v/>
+      </c>
+      <c r="H22" s="23">
+        <f>H19</f>
+        <v/>
+      </c>
+      <c r="I22" s="23">
+        <f>I19</f>
+        <v/>
+      </c>
+      <c r="J22" s="23">
+        <f>J19</f>
+        <v/>
+      </c>
+      <c r="K22" s="23">
+        <f>K19</f>
+        <v/>
+      </c>
+      <c r="L22" s="23">
+        <f>L19</f>
+        <v/>
+      </c>
+      <c r="M22" s="23">
+        <f>M19</f>
+        <v/>
+      </c>
+      <c r="N22" s="23">
+        <f>N19</f>
+        <v/>
+      </c>
+      <c r="O22" s="23">
+        <f>O19</f>
+        <v/>
+      </c>
+      <c r="P22" s="23">
+        <f>P19</f>
+        <v/>
+      </c>
+      <c r="Q22" s="23">
+        <f>Q19</f>
+        <v/>
+      </c>
+      <c r="R22" s="23">
+        <f>R19</f>
+        <v/>
+      </c>
+      <c r="S22" s="23">
+        <f>S19</f>
+        <v/>
+      </c>
+      <c r="T22" s="23">
+        <f>T19</f>
+        <v/>
+      </c>
+      <c r="U22" s="23">
+        <f>U19</f>
+        <v/>
+      </c>
+      <c r="V22" s="23">
+        <f>V19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Total interest</t>
+        </is>
+      </c>
+      <c r="C25" s="24">
+        <f>C13+C21</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>D13+D21</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>E13+E21</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>F13+F21</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>G13+G21</f>
+        <v/>
+      </c>
+      <c r="H25" s="24">
+        <f>H13+H21</f>
+        <v/>
+      </c>
+      <c r="I25" s="24">
+        <f>I13+I21</f>
+        <v/>
+      </c>
+      <c r="J25" s="24">
+        <f>J13+J21</f>
+        <v/>
+      </c>
+      <c r="K25" s="24">
+        <f>K13+K21</f>
+        <v/>
+      </c>
+      <c r="L25" s="24">
+        <f>L13+L21</f>
+        <v/>
+      </c>
+      <c r="M25" s="24">
+        <f>M13+M21</f>
+        <v/>
+      </c>
+      <c r="N25" s="24">
+        <f>N13+N21</f>
+        <v/>
+      </c>
+      <c r="O25" s="24">
+        <f>O13+O21</f>
+        <v/>
+      </c>
+      <c r="P25" s="24">
+        <f>P13+P21</f>
+        <v/>
+      </c>
+      <c r="Q25" s="24">
+        <f>Q13+Q21</f>
+        <v/>
+      </c>
+      <c r="R25" s="24">
+        <f>R13+R21</f>
+        <v/>
+      </c>
+      <c r="S25" s="24">
+        <f>S13+S21</f>
+        <v/>
+      </c>
+      <c r="T25" s="24">
+        <f>T13+T21</f>
+        <v/>
+      </c>
+      <c r="U25" s="24">
+        <f>U13+U21</f>
+        <v/>
+      </c>
+      <c r="V25" s="24">
+        <f>V13+V21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Total principal</t>
+        </is>
+      </c>
+      <c r="C26" s="24">
+        <f>C14+C20</f>
+        <v/>
+      </c>
+      <c r="D26" s="24">
+        <f>D14+D20</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>E14+E20</f>
+        <v/>
+      </c>
+      <c r="F26" s="24">
+        <f>F14+F20</f>
+        <v/>
+      </c>
+      <c r="G26" s="24">
+        <f>G14+G20</f>
+        <v/>
+      </c>
+      <c r="H26" s="24">
+        <f>H14+H20</f>
+        <v/>
+      </c>
+      <c r="I26" s="24">
+        <f>I14+I20</f>
+        <v/>
+      </c>
+      <c r="J26" s="24">
+        <f>J14+J20</f>
+        <v/>
+      </c>
+      <c r="K26" s="24">
+        <f>K14+K20</f>
+        <v/>
+      </c>
+      <c r="L26" s="24">
+        <f>L14+L20</f>
+        <v/>
+      </c>
+      <c r="M26" s="24">
+        <f>M14+M20</f>
+        <v/>
+      </c>
+      <c r="N26" s="24">
+        <f>N14+N20</f>
+        <v/>
+      </c>
+      <c r="O26" s="24">
+        <f>O14+O20</f>
+        <v/>
+      </c>
+      <c r="P26" s="24">
+        <f>P14+P20</f>
+        <v/>
+      </c>
+      <c r="Q26" s="24">
+        <f>Q14+Q20</f>
+        <v/>
+      </c>
+      <c r="R26" s="24">
+        <f>R14+R20</f>
+        <v/>
+      </c>
+      <c r="S26" s="24">
+        <f>S14+S20</f>
+        <v/>
+      </c>
+      <c r="T26" s="24">
+        <f>T14+T20</f>
+        <v/>
+      </c>
+      <c r="U26" s="24">
+        <f>U14+U20</f>
+        <v/>
+      </c>
+      <c r="V26" s="24">
+        <f>V14+V20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL DEBT SERVICE (P+I)</t>
+        </is>
+      </c>
+      <c r="C27" s="23">
+        <f>C25+C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="23">
+        <f>D25+D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="23">
+        <f>E25+E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="23">
+        <f>F25+F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="23">
+        <f>G25+G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="23">
+        <f>H25+H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="23">
+        <f>I25+I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="23">
+        <f>J25+J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="23">
+        <f>K25+K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="23">
+        <f>L25+L26</f>
+        <v/>
+      </c>
+      <c r="M27" s="23">
+        <f>M25+M26</f>
+        <v/>
+      </c>
+      <c r="N27" s="23">
+        <f>N25+N26</f>
+        <v/>
+      </c>
+      <c r="O27" s="23">
+        <f>O25+O26</f>
+        <v/>
+      </c>
+      <c r="P27" s="23">
+        <f>P25+P26</f>
+        <v/>
+      </c>
+      <c r="Q27" s="23">
+        <f>Q25+Q26</f>
+        <v/>
+      </c>
+      <c r="R27" s="23">
+        <f>R25+R26</f>
+        <v/>
+      </c>
+      <c r="S27" s="23">
+        <f>S25+S26</f>
+        <v/>
+      </c>
+      <c r="T27" s="23">
+        <f>T25+T26</f>
+        <v/>
+      </c>
+      <c r="U27" s="23">
+        <f>U25+U26</f>
+        <v/>
+      </c>
+      <c r="V27" s="23">
+        <f>V25+V26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>EBITDA (link)</t>
+        </is>
+      </c>
+      <c r="C28" s="25">
+        <f>'Operating Budget'!C24</f>
+        <v/>
+      </c>
+      <c r="D28" s="25">
+        <f>'Operating Budget'!D24</f>
+        <v/>
+      </c>
+      <c r="E28" s="25">
+        <f>'Operating Budget'!E24</f>
+        <v/>
+      </c>
+      <c r="F28" s="25">
+        <f>'Operating Budget'!F24</f>
+        <v/>
+      </c>
+      <c r="G28" s="25">
+        <f>'Operating Budget'!G24</f>
+        <v/>
+      </c>
+      <c r="H28" s="25">
+        <f>'Operating Budget'!H24</f>
+        <v/>
+      </c>
+      <c r="I28" s="25">
+        <f>'Operating Budget'!I24</f>
+        <v/>
+      </c>
+      <c r="J28" s="25">
+        <f>'Operating Budget'!J24</f>
+        <v/>
+      </c>
+      <c r="K28" s="25">
+        <f>'Operating Budget'!K24</f>
+        <v/>
+      </c>
+      <c r="L28" s="25">
+        <f>'Operating Budget'!L24</f>
+        <v/>
+      </c>
+      <c r="M28" s="25">
+        <f>'Operating Budget'!M24</f>
+        <v/>
+      </c>
+      <c r="N28" s="25">
+        <f>'Operating Budget'!N24</f>
+        <v/>
+      </c>
+      <c r="O28" s="25">
+        <f>'Operating Budget'!O24</f>
+        <v/>
+      </c>
+      <c r="P28" s="25">
+        <f>'Operating Budget'!P24</f>
+        <v/>
+      </c>
+      <c r="Q28" s="25">
+        <f>'Operating Budget'!Q24</f>
+        <v/>
+      </c>
+      <c r="R28" s="25">
+        <f>'Operating Budget'!R24</f>
+        <v/>
+      </c>
+      <c r="S28" s="25">
+        <f>'Operating Budget'!S24</f>
+        <v/>
+      </c>
+      <c r="T28" s="25">
+        <f>'Operating Budget'!T24</f>
+        <v/>
+      </c>
+      <c r="U28" s="25">
+        <f>'Operating Budget'!U24</f>
+        <v/>
+      </c>
+      <c r="V28" s="25">
+        <f>'Operating Budget'!V24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>DSCR (period)</t>
+        </is>
+      </c>
+      <c r="C29" s="57">
+        <f>IF(C27=0,0,C28/C27)</f>
+        <v/>
+      </c>
+      <c r="D29" s="57">
+        <f>IF(D27=0,0,D28/D27)</f>
+        <v/>
+      </c>
+      <c r="E29" s="57">
+        <f>IF(E27=0,0,E28/E27)</f>
+        <v/>
+      </c>
+      <c r="F29" s="57">
+        <f>IF(F27=0,0,F28/F27)</f>
+        <v/>
+      </c>
+      <c r="G29" s="57">
+        <f>IF(G27=0,0,G28/G27)</f>
+        <v/>
+      </c>
+      <c r="H29" s="57">
+        <f>IF(H27=0,0,H28/H27)</f>
+        <v/>
+      </c>
+      <c r="I29" s="57">
+        <f>IF(I27=0,0,I28/I27)</f>
+        <v/>
+      </c>
+      <c r="J29" s="57">
+        <f>IF(J27=0,0,J28/J27)</f>
+        <v/>
+      </c>
+      <c r="K29" s="57">
+        <f>IF(K27=0,0,K28/K27)</f>
+        <v/>
+      </c>
+      <c r="L29" s="57">
+        <f>IF(L27=0,0,L28/L27)</f>
+        <v/>
+      </c>
+      <c r="M29" s="57">
+        <f>IF(M27=0,0,M28/M27)</f>
+        <v/>
+      </c>
+      <c r="N29" s="57">
+        <f>IF(N27=0,0,N28/N27)</f>
+        <v/>
+      </c>
+      <c r="O29" s="57">
+        <f>IF(O27=0,0,O28/O27)</f>
+        <v/>
+      </c>
+      <c r="P29" s="57">
+        <f>IF(P27=0,0,P28/P27)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="57">
+        <f>IF(Q27=0,0,Q28/Q27)</f>
+        <v/>
+      </c>
+      <c r="R29" s="57">
+        <f>IF(R27=0,0,R28/R27)</f>
+        <v/>
+      </c>
+      <c r="S29" s="57">
+        <f>IF(S27=0,0,S28/S27)</f>
+        <v/>
+      </c>
+      <c r="T29" s="57">
+        <f>IF(T27=0,0,T28/T27)</f>
+        <v/>
+      </c>
+      <c r="U29" s="57">
+        <f>IF(U27=0,0,U28/U27)</f>
+        <v/>
+      </c>
+      <c r="V29" s="57">
+        <f>IF(V27=0,0,V28/V27)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A10:V10"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="A17:V17"/>
+    <mergeCell ref="C8:N8"/>
+    <mergeCell ref="A4:V4"/>
+    <mergeCell ref="A24:V24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3730,34 +5290,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Opening</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="41" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="41" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr"/>
+      <c r="A5" s="43" t="inlineStr"/>
       <c r="C5" s="30" t="inlineStr">
         <is>
           <t>M1</t>
@@ -5110,83 +6670,83 @@
           <t>ENDING CASH</t>
         </is>
       </c>
-      <c r="C21" s="45">
+      <c r="C21" s="46">
         <f>C18+C19</f>
         <v/>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="46">
         <f>D18+D19</f>
         <v/>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="46">
         <f>E18+E19</f>
         <v/>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="46">
         <f>F18+F19</f>
         <v/>
       </c>
-      <c r="G21" s="45">
+      <c r="G21" s="46">
         <f>G18+G19</f>
         <v/>
       </c>
-      <c r="H21" s="45">
+      <c r="H21" s="46">
         <f>H18+H19</f>
         <v/>
       </c>
-      <c r="I21" s="45">
+      <c r="I21" s="46">
         <f>I18+I19</f>
         <v/>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="46">
         <f>J18+J19</f>
         <v/>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="46">
         <f>K18+K19</f>
         <v/>
       </c>
-      <c r="L21" s="45">
+      <c r="L21" s="46">
         <f>L18+L19</f>
         <v/>
       </c>
-      <c r="M21" s="45">
+      <c r="M21" s="46">
         <f>M18+M19</f>
         <v/>
       </c>
-      <c r="N21" s="45">
+      <c r="N21" s="46">
         <f>N18+N19</f>
         <v/>
       </c>
-      <c r="O21" s="45">
+      <c r="O21" s="46">
         <f>O18+O19</f>
         <v/>
       </c>
-      <c r="P21" s="45">
+      <c r="P21" s="46">
         <f>P18+P19</f>
         <v/>
       </c>
-      <c r="Q21" s="45">
+      <c r="Q21" s="46">
         <f>Q18+Q19</f>
         <v/>
       </c>
-      <c r="R21" s="45">
+      <c r="R21" s="46">
         <f>R18+R19</f>
         <v/>
       </c>
-      <c r="S21" s="45">
+      <c r="S21" s="46">
         <f>S18+S19</f>
         <v/>
       </c>
-      <c r="T21" s="45">
+      <c r="T21" s="46">
         <f>T18+T19</f>
         <v/>
       </c>
-      <c r="U21" s="45">
+      <c r="U21" s="46">
         <f>U18+U19</f>
         <v/>
       </c>
-      <c r="V21" s="45">
+      <c r="V21" s="46">
         <f>V18+V19</f>
         <v/>
       </c>
@@ -6486,7 +8046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -6588,7 +8148,7 @@
         <f>'Revenue Model'!E14</f>
         <v/>
       </c>
-      <c r="H5" s="46">
+      <c r="H5" s="39">
         <f>IF(F5=0,0,(G5-F5)/F5)</f>
         <v/>
       </c>
@@ -6700,11 +8260,11 @@
         <f>AVERAGE(C9:E9)</f>
         <v/>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="44">
         <f>'Revenue Model'!E10</f>
         <v/>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="39">
         <f>IF(F9=0,0,(G9-F9)/F9)</f>
         <v/>
       </c>
@@ -6742,7 +8302,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="H12" s="46">
+      <c r="H12" s="39">
         <f>IF(F12=0,0,(G12-F12)/F12)</f>
         <v/>
       </c>
@@ -6773,7 +8333,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="H13" s="46">
+      <c r="H13" s="39">
         <f>IF(F13=0,0,(G13-F13)/F13)</f>
         <v/>
       </c>
@@ -6804,7 +8364,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="39">
         <f>IF(F14=0,0,(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -7743,6 +9303,360 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AZALEA HOSPICE &amp; PALLIATIVE CARE - Tyler, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MVI 'Perfect Visit' Upside - illustrative growth above the conservative base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMPTION (blue = adjust)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MVI-driven census / referral uplift %</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SCENARIO RESULTS (Year-2 annualized, SBA-only debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Base (plan)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>+30%</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>MVI case</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Census / referral uplift</t>
+        </is>
+      </c>
+      <c r="B9" s="39">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C9" s="39">
+        <f>0.10</f>
+        <v/>
+      </c>
+      <c r="D9" s="39">
+        <f>0.20</f>
+        <v/>
+      </c>
+      <c r="E9" s="39">
+        <f>0.30</f>
+        <v/>
+      </c>
+      <c r="F9" s="39">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Variable costs</t>
+        </is>
+      </c>
+      <c r="B11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+B9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+C9)</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+D9)</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Fixed costs (held at plan)</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B13" s="27">
+        <f>B10+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="27">
+        <f>E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="27">
+        <f>F10+F11+F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>EBITDA lift vs base</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>B13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>C13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>D13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>E13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>F13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Net income (after D&amp;A, interest, tax)</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(B13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*B9</f>
+        <v/>
+      </c>
+      <c r="C15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(C13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(D13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*D9</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(E13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*E9</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(F13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>SBA debt service</t>
+        </is>
+      </c>
+      <c r="B16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>DSCR (SBA-only)</t>
+        </is>
+      </c>
+      <c r="B17" s="34">
+        <f>IF(B16=0,0,B13/B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="34">
+        <f>IF(C16=0,0,C13/C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="34">
+        <f>IF(D16=0,0,D13/D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="34">
+        <f>IF(E16=0,0,E13/E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(F16=0,0,F13/F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Illustrative upside ONLY - not used for loan underwriting. The base case (Lender Summary / Business Plan Section 11) assumes no lift from the MVI 'Perfect Visit' / 'Perfect Phones' certification or Andrew Reid's national advertising campaign; SBA debt service is fully covered without it. This tab scales Year-2 census/referrals by the uplift while holding the cost base at plan (static roster); sustained higher census would trigger the model's capacity hiring, so realized EBITDA would run modestly below the static figures shown. Higher EBITDA also raises the equity exit value and MOIC on the Returns tab. For a full dynamic re-run, set Census scenario = Upside on the Inputs tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F22"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -7803,7 +9717,7 @@
           <t>Blended GROSS rate ($/PD)</t>
         </is>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="40">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
@@ -7814,35 +9728,35 @@
           <t>Blended NET rate ($/PD)</t>
         </is>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="40">
         <f>Inputs!$B$21</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O8" s="41" t="inlineStr">
+      <c r="O8" s="42" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S8" s="41" t="inlineStr">
+      <c r="S8" s="42" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="inlineStr"/>
+      <c r="A9" s="43" t="inlineStr"/>
       <c r="C9" s="30" t="inlineStr">
         <is>
           <t>M1</t>
@@ -7950,83 +9864,83 @@
           <t>Average daily census (ADC)</t>
         </is>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="44">
         <f>Inputs!C$33</f>
         <v/>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="44">
         <f>Inputs!D$33</f>
         <v/>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <f>Inputs!E$33</f>
         <v/>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="44">
         <f>Inputs!F$33</f>
         <v/>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="44">
         <f>Inputs!G$33</f>
         <v/>
       </c>
-      <c r="H10" s="43">
+      <c r="H10" s="44">
         <f>Inputs!H$33</f>
         <v/>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="44">
         <f>Inputs!I$33</f>
         <v/>
       </c>
-      <c r="J10" s="43">
+      <c r="J10" s="44">
         <f>Inputs!J$33</f>
         <v/>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="44">
         <f>Inputs!K$33</f>
         <v/>
       </c>
-      <c r="L10" s="43">
+      <c r="L10" s="44">
         <f>Inputs!L$33</f>
         <v/>
       </c>
-      <c r="M10" s="43">
+      <c r="M10" s="44">
         <f>Inputs!M$33</f>
         <v/>
       </c>
-      <c r="N10" s="43">
+      <c r="N10" s="44">
         <f>Inputs!N$33</f>
         <v/>
       </c>
-      <c r="O10" s="43">
+      <c r="O10" s="44">
         <f>Inputs!O$33</f>
         <v/>
       </c>
-      <c r="P10" s="43">
+      <c r="P10" s="44">
         <f>Inputs!P$33</f>
         <v/>
       </c>
-      <c r="Q10" s="43">
+      <c r="Q10" s="44">
         <f>Inputs!Q$33</f>
         <v/>
       </c>
-      <c r="R10" s="43">
+      <c r="R10" s="44">
         <f>Inputs!R$33</f>
         <v/>
       </c>
-      <c r="S10" s="43">
+      <c r="S10" s="44">
         <f>Inputs!S$33</f>
         <v/>
       </c>
-      <c r="T10" s="43">
+      <c r="T10" s="44">
         <f>Inputs!T$33</f>
         <v/>
       </c>
-      <c r="U10" s="43">
+      <c r="U10" s="44">
         <f>Inputs!U$33</f>
         <v/>
       </c>
-      <c r="V10" s="43">
+      <c r="V10" s="44">
         <f>Inputs!V$33</f>
         <v/>
       </c>
@@ -8037,83 +9951,83 @@
           <t>Days in period</t>
         </is>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="J11" s="43">
+      <c r="J11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="N11" s="43">
+      <c r="N11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="O11" s="43">
+      <c r="O11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="P11" s="43">
+      <c r="P11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="Q11" s="43">
+      <c r="Q11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="R11" s="43">
+      <c r="R11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="S11" s="43">
+      <c r="S11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="T11" s="43">
+      <c r="T11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="U11" s="43">
+      <c r="U11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="V11" s="43">
+      <c r="V11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
@@ -8124,83 +10038,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="45">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="45">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="45">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="45">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="45">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="45">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="45">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="44">
+      <c r="J12" s="45">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="45">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="44">
+      <c r="L12" s="45">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="44">
+      <c r="M12" s="45">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="44">
+      <c r="N12" s="45">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="44">
+      <c r="O12" s="45">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="45">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="44">
+      <c r="Q12" s="45">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="44">
+      <c r="R12" s="45">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="44">
+      <c r="S12" s="45">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="44">
+      <c r="T12" s="45">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="44">
+      <c r="U12" s="45">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="44">
+      <c r="V12" s="45">
         <f>V10*V11</f>
         <v/>
       </c>
@@ -8559,83 +10473,83 @@
           <t>NET REVENUE</t>
         </is>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="46">
         <f>C14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="46">
         <f>D14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="46">
         <f>E14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="46">
         <f>F14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="46">
         <f>G14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="46">
         <f>H14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="46">
         <f>I14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="46">
         <f>J14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="46">
         <f>K14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="L17" s="45">
+      <c r="L17" s="46">
         <f>L14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="M17" s="45">
+      <c r="M17" s="46">
         <f>M14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="N17" s="45">
+      <c r="N17" s="46">
         <f>N14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="O17" s="45">
+      <c r="O17" s="46">
         <f>O14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="P17" s="45">
+      <c r="P17" s="46">
         <f>P14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="Q17" s="45">
+      <c r="Q17" s="46">
         <f>Q14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="R17" s="45">
+      <c r="R17" s="46">
         <f>R14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="S17" s="45">
+      <c r="S17" s="46">
         <f>S14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="T17" s="45">
+      <c r="T17" s="46">
         <f>T14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="U17" s="45">
+      <c r="U17" s="46">
         <f>U14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="V17" s="45">
+      <c r="V17" s="46">
         <f>V14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
@@ -8740,7 +10654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -8789,29 +10703,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="41" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="41" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr"/>
+      <c r="A5" s="43" t="inlineStr"/>
       <c r="C5" s="30" t="inlineStr">
         <is>
           <t>M1</t>
@@ -8919,83 +10833,83 @@
           <t>ADC (driver)</t>
         </is>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="44">
         <f>'Revenue Model'!C10</f>
         <v/>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="44">
         <f>'Revenue Model'!D10</f>
         <v/>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="44">
         <f>'Revenue Model'!E10</f>
         <v/>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="44">
         <f>'Revenue Model'!F10</f>
         <v/>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="44">
         <f>'Revenue Model'!G10</f>
         <v/>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="44">
         <f>'Revenue Model'!H10</f>
         <v/>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="44">
         <f>'Revenue Model'!I10</f>
         <v/>
       </c>
-      <c r="J6" s="43">
+      <c r="J6" s="44">
         <f>'Revenue Model'!J10</f>
         <v/>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="44">
         <f>'Revenue Model'!K10</f>
         <v/>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="44">
         <f>'Revenue Model'!L10</f>
         <v/>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="44">
         <f>'Revenue Model'!M10</f>
         <v/>
       </c>
-      <c r="N6" s="43">
+      <c r="N6" s="44">
         <f>'Revenue Model'!N10</f>
         <v/>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="44">
         <f>'Revenue Model'!O10</f>
         <v/>
       </c>
-      <c r="P6" s="43">
+      <c r="P6" s="44">
         <f>'Revenue Model'!P10</f>
         <v/>
       </c>
-      <c r="Q6" s="43">
+      <c r="Q6" s="44">
         <f>'Revenue Model'!Q10</f>
         <v/>
       </c>
-      <c r="R6" s="43">
+      <c r="R6" s="44">
         <f>'Revenue Model'!R10</f>
         <v/>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="44">
         <f>'Revenue Model'!S10</f>
         <v/>
       </c>
-      <c r="T6" s="43">
+      <c r="T6" s="44">
         <f>'Revenue Model'!T10</f>
         <v/>
       </c>
-      <c r="U6" s="43">
+      <c r="U6" s="44">
         <f>'Revenue Model'!U10</f>
         <v/>
       </c>
-      <c r="V6" s="43">
+      <c r="V6" s="44">
         <f>'Revenue Model'!V10</f>
         <v/>
       </c>
@@ -12340,83 +14254,83 @@
           <t>TOTAL DIRECT-CARE LABOR (COGS)</t>
         </is>
       </c>
-      <c r="C53" s="45">
+      <c r="C53" s="46">
         <f>C30+C38+C39+C48+C50</f>
         <v/>
       </c>
-      <c r="D53" s="45">
+      <c r="D53" s="46">
         <f>D30+D38+D39+D48+D50</f>
         <v/>
       </c>
-      <c r="E53" s="45">
+      <c r="E53" s="46">
         <f>E30+E38+E39+E48+E50</f>
         <v/>
       </c>
-      <c r="F53" s="45">
+      <c r="F53" s="46">
         <f>F30+F38+F39+F48+F50</f>
         <v/>
       </c>
-      <c r="G53" s="45">
+      <c r="G53" s="46">
         <f>G30+G38+G39+G48+G50</f>
         <v/>
       </c>
-      <c r="H53" s="45">
+      <c r="H53" s="46">
         <f>H30+H38+H39+H48+H50</f>
         <v/>
       </c>
-      <c r="I53" s="45">
+      <c r="I53" s="46">
         <f>I30+I38+I39+I48+I50</f>
         <v/>
       </c>
-      <c r="J53" s="45">
+      <c r="J53" s="46">
         <f>J30+J38+J39+J48+J50</f>
         <v/>
       </c>
-      <c r="K53" s="45">
+      <c r="K53" s="46">
         <f>K30+K38+K39+K48+K50</f>
         <v/>
       </c>
-      <c r="L53" s="45">
+      <c r="L53" s="46">
         <f>L30+L38+L39+L48+L50</f>
         <v/>
       </c>
-      <c r="M53" s="45">
+      <c r="M53" s="46">
         <f>M30+M38+M39+M48+M50</f>
         <v/>
       </c>
-      <c r="N53" s="45">
+      <c r="N53" s="46">
         <f>N30+N38+N39+N48+N50</f>
         <v/>
       </c>
-      <c r="O53" s="45">
+      <c r="O53" s="46">
         <f>O30+O38+O39+O48+O50</f>
         <v/>
       </c>
-      <c r="P53" s="45">
+      <c r="P53" s="46">
         <f>P30+P38+P39+P48+P50</f>
         <v/>
       </c>
-      <c r="Q53" s="45">
+      <c r="Q53" s="46">
         <f>Q30+Q38+Q39+Q48+Q50</f>
         <v/>
       </c>
-      <c r="R53" s="45">
+      <c r="R53" s="46">
         <f>R30+R38+R39+R48+R50</f>
         <v/>
       </c>
-      <c r="S53" s="45">
+      <c r="S53" s="46">
         <f>S30+S38+S39+S48+S50</f>
         <v/>
       </c>
-      <c r="T53" s="45">
+      <c r="T53" s="46">
         <f>T30+T38+T39+T48+T50</f>
         <v/>
       </c>
-      <c r="U53" s="45">
+      <c r="U53" s="46">
         <f>U30+U38+U39+U48+U50</f>
         <v/>
       </c>
-      <c r="V53" s="45">
+      <c r="V53" s="46">
         <f>V30+V38+V39+V48+V50</f>
         <v/>
       </c>
@@ -12427,83 +14341,83 @@
           <t>TOTAL INDIRECT LABOR (SG&amp;A)</t>
         </is>
       </c>
-      <c r="C54" s="45">
+      <c r="C54" s="46">
         <f>C42+C43+C49+C51</f>
         <v/>
       </c>
-      <c r="D54" s="45">
+      <c r="D54" s="46">
         <f>D42+D43+D49+D51</f>
         <v/>
       </c>
-      <c r="E54" s="45">
+      <c r="E54" s="46">
         <f>E42+E43+E49+E51</f>
         <v/>
       </c>
-      <c r="F54" s="45">
+      <c r="F54" s="46">
         <f>F42+F43+F49+F51</f>
         <v/>
       </c>
-      <c r="G54" s="45">
+      <c r="G54" s="46">
         <f>G42+G43+G49+G51</f>
         <v/>
       </c>
-      <c r="H54" s="45">
+      <c r="H54" s="46">
         <f>H42+H43+H49+H51</f>
         <v/>
       </c>
-      <c r="I54" s="45">
+      <c r="I54" s="46">
         <f>I42+I43+I49+I51</f>
         <v/>
       </c>
-      <c r="J54" s="45">
+      <c r="J54" s="46">
         <f>J42+J43+J49+J51</f>
         <v/>
       </c>
-      <c r="K54" s="45">
+      <c r="K54" s="46">
         <f>K42+K43+K49+K51</f>
         <v/>
       </c>
-      <c r="L54" s="45">
+      <c r="L54" s="46">
         <f>L42+L43+L49+L51</f>
         <v/>
       </c>
-      <c r="M54" s="45">
+      <c r="M54" s="46">
         <f>M42+M43+M49+M51</f>
         <v/>
       </c>
-      <c r="N54" s="45">
+      <c r="N54" s="46">
         <f>N42+N43+N49+N51</f>
         <v/>
       </c>
-      <c r="O54" s="45">
+      <c r="O54" s="46">
         <f>O42+O43+O49+O51</f>
         <v/>
       </c>
-      <c r="P54" s="45">
+      <c r="P54" s="46">
         <f>P42+P43+P49+P51</f>
         <v/>
       </c>
-      <c r="Q54" s="45">
+      <c r="Q54" s="46">
         <f>Q42+Q43+Q49+Q51</f>
         <v/>
       </c>
-      <c r="R54" s="45">
+      <c r="R54" s="46">
         <f>R42+R43+R49+R51</f>
         <v/>
       </c>
-      <c r="S54" s="45">
+      <c r="S54" s="46">
         <f>S42+S43+S49+S51</f>
         <v/>
       </c>
-      <c r="T54" s="45">
+      <c r="T54" s="46">
         <f>T42+T43+T49+T51</f>
         <v/>
       </c>
-      <c r="U54" s="45">
+      <c r="U54" s="46">
         <f>U42+U43+U49+U51</f>
         <v/>
       </c>
-      <c r="V54" s="45">
+      <c r="V54" s="46">
         <f>V42+V43+V49+V51</f>
         <v/>
       </c>
@@ -12524,7 +14438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -12573,29 +14487,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="41" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="41" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr"/>
+      <c r="A5" s="43" t="inlineStr"/>
       <c r="C5" s="30" t="inlineStr">
         <is>
           <t>M1</t>
@@ -13319,83 +15233,83 @@
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="C15" s="45">
+      <c r="C15" s="46">
         <f>C6-C14</f>
         <v/>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="46">
         <f>D6-D14</f>
         <v/>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="46">
         <f>E6-E14</f>
         <v/>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="46">
         <f>F6-F14</f>
         <v/>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="46">
         <f>G6-G14</f>
         <v/>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="46">
         <f>H6-H14</f>
         <v/>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="46">
         <f>I6-I14</f>
         <v/>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="46">
         <f>J6-J14</f>
         <v/>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="46">
         <f>K6-K14</f>
         <v/>
       </c>
-      <c r="L15" s="45">
+      <c r="L15" s="46">
         <f>L6-L14</f>
         <v/>
       </c>
-      <c r="M15" s="45">
+      <c r="M15" s="46">
         <f>M6-M14</f>
         <v/>
       </c>
-      <c r="N15" s="45">
+      <c r="N15" s="46">
         <f>N6-N14</f>
         <v/>
       </c>
-      <c r="O15" s="45">
+      <c r="O15" s="46">
         <f>O6-O14</f>
         <v/>
       </c>
-      <c r="P15" s="45">
+      <c r="P15" s="46">
         <f>P6-P14</f>
         <v/>
       </c>
-      <c r="Q15" s="45">
+      <c r="Q15" s="46">
         <f>Q6-Q14</f>
         <v/>
       </c>
-      <c r="R15" s="45">
+      <c r="R15" s="46">
         <f>R6-R14</f>
         <v/>
       </c>
-      <c r="S15" s="45">
+      <c r="S15" s="46">
         <f>S6-S14</f>
         <v/>
       </c>
-      <c r="T15" s="45">
+      <c r="T15" s="46">
         <f>T6-T14</f>
         <v/>
       </c>
-      <c r="U15" s="45">
+      <c r="U15" s="46">
         <f>U6-U14</f>
         <v/>
       </c>
-      <c r="V15" s="45">
+      <c r="V15" s="46">
         <f>V6-V14</f>
         <v/>
       </c>
@@ -13406,83 +15320,83 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="39">
         <f>IF(C6=0,0,C15/C6)</f>
         <v/>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="39">
         <f>IF(D6=0,0,D15/D6)</f>
         <v/>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="39">
         <f>IF(E6=0,0,E15/E6)</f>
         <v/>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="39">
         <f>IF(F6=0,0,F15/F6)</f>
         <v/>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="39">
         <f>IF(G6=0,0,G15/G6)</f>
         <v/>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="39">
         <f>IF(H6=0,0,H15/H6)</f>
         <v/>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="39">
         <f>IF(I6=0,0,I15/I6)</f>
         <v/>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="39">
         <f>IF(J6=0,0,J15/J6)</f>
         <v/>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="39">
         <f>IF(K6=0,0,K15/K6)</f>
         <v/>
       </c>
-      <c r="L16" s="46">
+      <c r="L16" s="39">
         <f>IF(L6=0,0,L15/L6)</f>
         <v/>
       </c>
-      <c r="M16" s="46">
+      <c r="M16" s="39">
         <f>IF(M6=0,0,M15/M6)</f>
         <v/>
       </c>
-      <c r="N16" s="46">
+      <c r="N16" s="39">
         <f>IF(N6=0,0,N15/N6)</f>
         <v/>
       </c>
-      <c r="O16" s="46">
+      <c r="O16" s="39">
         <f>IF(O6=0,0,O15/O6)</f>
         <v/>
       </c>
-      <c r="P16" s="46">
+      <c r="P16" s="39">
         <f>IF(P6=0,0,P15/P6)</f>
         <v/>
       </c>
-      <c r="Q16" s="46">
+      <c r="Q16" s="39">
         <f>IF(Q6=0,0,Q15/Q6)</f>
         <v/>
       </c>
-      <c r="R16" s="46">
+      <c r="R16" s="39">
         <f>IF(R6=0,0,R15/R6)</f>
         <v/>
       </c>
-      <c r="S16" s="46">
+      <c r="S16" s="39">
         <f>IF(S6=0,0,S15/S6)</f>
         <v/>
       </c>
-      <c r="T16" s="46">
+      <c r="T16" s="39">
         <f>IF(T6=0,0,T15/T6)</f>
         <v/>
       </c>
-      <c r="U16" s="46">
+      <c r="U16" s="39">
         <f>IF(U6=0,0,U15/U6)</f>
         <v/>
       </c>
-      <c r="V16" s="46">
+      <c r="V16" s="39">
         <f>IF(V6=0,0,V15/V6)</f>
         <v/>
       </c>
@@ -14022,83 +15936,83 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="39">
         <f>IF(C6=0,0,C24/C6)</f>
         <v/>
       </c>
-      <c r="D25" s="46">
+      <c r="D25" s="39">
         <f>IF(D6=0,0,D24/D6)</f>
         <v/>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="39">
         <f>IF(E6=0,0,E24/E6)</f>
         <v/>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="39">
         <f>IF(F6=0,0,F24/F6)</f>
         <v/>
       </c>
-      <c r="G25" s="46">
+      <c r="G25" s="39">
         <f>IF(G6=0,0,G24/G6)</f>
         <v/>
       </c>
-      <c r="H25" s="46">
+      <c r="H25" s="39">
         <f>IF(H6=0,0,H24/H6)</f>
         <v/>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="39">
         <f>IF(I6=0,0,I24/I6)</f>
         <v/>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="39">
         <f>IF(J6=0,0,J24/J6)</f>
         <v/>
       </c>
-      <c r="K25" s="46">
+      <c r="K25" s="39">
         <f>IF(K6=0,0,K24/K6)</f>
         <v/>
       </c>
-      <c r="L25" s="46">
+      <c r="L25" s="39">
         <f>IF(L6=0,0,L24/L6)</f>
         <v/>
       </c>
-      <c r="M25" s="46">
+      <c r="M25" s="39">
         <f>IF(M6=0,0,M24/M6)</f>
         <v/>
       </c>
-      <c r="N25" s="46">
+      <c r="N25" s="39">
         <f>IF(N6=0,0,N24/N6)</f>
         <v/>
       </c>
-      <c r="O25" s="46">
+      <c r="O25" s="39">
         <f>IF(O6=0,0,O24/O6)</f>
         <v/>
       </c>
-      <c r="P25" s="46">
+      <c r="P25" s="39">
         <f>IF(P6=0,0,P24/P6)</f>
         <v/>
       </c>
-      <c r="Q25" s="46">
+      <c r="Q25" s="39">
         <f>IF(Q6=0,0,Q24/Q6)</f>
         <v/>
       </c>
-      <c r="R25" s="46">
+      <c r="R25" s="39">
         <f>IF(R6=0,0,R24/R6)</f>
         <v/>
       </c>
-      <c r="S25" s="46">
+      <c r="S25" s="39">
         <f>IF(S6=0,0,S24/S6)</f>
         <v/>
       </c>
-      <c r="T25" s="46">
+      <c r="T25" s="39">
         <f>IF(T6=0,0,T24/T6)</f>
         <v/>
       </c>
-      <c r="U25" s="46">
+      <c r="U25" s="39">
         <f>IF(U6=0,0,U24/U6)</f>
         <v/>
       </c>
-      <c r="V25" s="46">
+      <c r="V25" s="39">
         <f>IF(V6=0,0,V24/V6)</f>
         <v/>
       </c>
@@ -14638,83 +16552,83 @@
           <t>NET INCOME</t>
         </is>
       </c>
-      <c r="C34" s="45">
+      <c r="C34" s="46">
         <f>C32-C33</f>
         <v/>
       </c>
-      <c r="D34" s="45">
+      <c r="D34" s="46">
         <f>D32-D33</f>
         <v/>
       </c>
-      <c r="E34" s="45">
+      <c r="E34" s="46">
         <f>E32-E33</f>
         <v/>
       </c>
-      <c r="F34" s="45">
+      <c r="F34" s="46">
         <f>F32-F33</f>
         <v/>
       </c>
-      <c r="G34" s="45">
+      <c r="G34" s="46">
         <f>G32-G33</f>
         <v/>
       </c>
-      <c r="H34" s="45">
+      <c r="H34" s="46">
         <f>H32-H33</f>
         <v/>
       </c>
-      <c r="I34" s="45">
+      <c r="I34" s="46">
         <f>I32-I33</f>
         <v/>
       </c>
-      <c r="J34" s="45">
+      <c r="J34" s="46">
         <f>J32-J33</f>
         <v/>
       </c>
-      <c r="K34" s="45">
+      <c r="K34" s="46">
         <f>K32-K33</f>
         <v/>
       </c>
-      <c r="L34" s="45">
+      <c r="L34" s="46">
         <f>L32-L33</f>
         <v/>
       </c>
-      <c r="M34" s="45">
+      <c r="M34" s="46">
         <f>M32-M33</f>
         <v/>
       </c>
-      <c r="N34" s="45">
+      <c r="N34" s="46">
         <f>N32-N33</f>
         <v/>
       </c>
-      <c r="O34" s="45">
+      <c r="O34" s="46">
         <f>O32-O33</f>
         <v/>
       </c>
-      <c r="P34" s="45">
+      <c r="P34" s="46">
         <f>P32-P33</f>
         <v/>
       </c>
-      <c r="Q34" s="45">
+      <c r="Q34" s="46">
         <f>Q32-Q33</f>
         <v/>
       </c>
-      <c r="R34" s="45">
+      <c r="R34" s="46">
         <f>R32-R33</f>
         <v/>
       </c>
-      <c r="S34" s="45">
+      <c r="S34" s="46">
         <f>S32-S33</f>
         <v/>
       </c>
-      <c r="T34" s="45">
+      <c r="T34" s="46">
         <f>T32-T33</f>
         <v/>
       </c>
-      <c r="U34" s="45">
+      <c r="U34" s="46">
         <f>U32-U33</f>
         <v/>
       </c>
-      <c r="V34" s="45">
+      <c r="V34" s="46">
         <f>V32-V33</f>
         <v/>
       </c>
@@ -14734,7 +16648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -18393,1548 +20307,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00808080"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:V29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AZALEA HOSPICE &amp; PALLIATIVE CARE - Tyler, TX</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>LOAN TERMS (from Inputs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SBA monthly payment (PMT)</t>
-        </is>
-      </c>
-      <c r="B5" s="24">
-        <f>PMT(Inputs!$B$111/12,Inputs!$B$112,-Inputs!$B$110)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>License note monthly payment (PMT)</t>
-        </is>
-      </c>
-      <c r="B6" s="24">
-        <f>0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
-        <is>
-          <t>($ per period)</t>
-        </is>
-      </c>
-      <c r="C8" s="41" t="inlineStr">
-        <is>
-          <t>YEAR 1 - monthly</t>
-        </is>
-      </c>
-      <c r="O8" s="41" t="inlineStr">
-        <is>
-          <t>YEAR 2 - quarterly</t>
-        </is>
-      </c>
-      <c r="S8" s="41" t="inlineStr">
-        <is>
-          <t>YEAR 3 - quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="42" t="inlineStr"/>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="F9" s="30" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="H9" s="30" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="J9" s="30" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="L9" s="30" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="M9" s="30" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="N9" s="30" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="O9" s="30" t="inlineStr">
-        <is>
-          <t>Y2 Q1</t>
-        </is>
-      </c>
-      <c r="P9" s="30" t="inlineStr">
-        <is>
-          <t>Y2 Q2</t>
-        </is>
-      </c>
-      <c r="Q9" s="30" t="inlineStr">
-        <is>
-          <t>Y2 Q3</t>
-        </is>
-      </c>
-      <c r="R9" s="30" t="inlineStr">
-        <is>
-          <t>Y2 Q4</t>
-        </is>
-      </c>
-      <c r="S9" s="30" t="inlineStr">
-        <is>
-          <t>Y3 Q1</t>
-        </is>
-      </c>
-      <c r="T9" s="30" t="inlineStr">
-        <is>
-          <t>Y3 Q2</t>
-        </is>
-      </c>
-      <c r="U9" s="30" t="inlineStr">
-        <is>
-          <t>Y3 Q3</t>
-        </is>
-      </c>
-      <c r="V9" s="30" t="inlineStr">
-        <is>
-          <t>Y3 Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>SBA 7(a) LOAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Beginning balance</t>
-        </is>
-      </c>
-      <c r="C11" s="25">
-        <f>Inputs!$B$110</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>C15</f>
-        <v/>
-      </c>
-      <c r="E11" s="24">
-        <f>D15</f>
-        <v/>
-      </c>
-      <c r="F11" s="24">
-        <f>E15</f>
-        <v/>
-      </c>
-      <c r="G11" s="24">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="H11" s="24">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="I11" s="24">
-        <f>H15</f>
-        <v/>
-      </c>
-      <c r="J11" s="24">
-        <f>I15</f>
-        <v/>
-      </c>
-      <c r="K11" s="24">
-        <f>J15</f>
-        <v/>
-      </c>
-      <c r="L11" s="24">
-        <f>K15</f>
-        <v/>
-      </c>
-      <c r="M11" s="24">
-        <f>L15</f>
-        <v/>
-      </c>
-      <c r="N11" s="24">
-        <f>M15</f>
-        <v/>
-      </c>
-      <c r="O11" s="24">
-        <f>N15</f>
-        <v/>
-      </c>
-      <c r="P11" s="24">
-        <f>O15</f>
-        <v/>
-      </c>
-      <c r="Q11" s="24">
-        <f>P15</f>
-        <v/>
-      </c>
-      <c r="R11" s="24">
-        <f>Q15</f>
-        <v/>
-      </c>
-      <c r="S11" s="24">
-        <f>R15</f>
-        <v/>
-      </c>
-      <c r="T11" s="24">
-        <f>S15</f>
-        <v/>
-      </c>
-      <c r="U11" s="24">
-        <f>T15</f>
-        <v/>
-      </c>
-      <c r="V11" s="24">
-        <f>U15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Payment</t>
-        </is>
-      </c>
-      <c r="C12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="F12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="G12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="H12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="I12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="J12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="K12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="L12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="M12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="N12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="O12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="P12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="Q12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="R12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="S12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="T12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="U12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="V12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="C13" s="24">
-        <f>C11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>D11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="E13" s="24">
-        <f>E11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="F13" s="24">
-        <f>F11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="G13" s="24">
-        <f>G11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="H13" s="24">
-        <f>H11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="I13" s="24">
-        <f>I11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="J13" s="24">
-        <f>J11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="K13" s="24">
-        <f>K11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="L13" s="24">
-        <f>L11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="M13" s="24">
-        <f>M11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="N13" s="24">
-        <f>N11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="O13" s="24">
-        <f>O11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="P13" s="24">
-        <f>P11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="Q13" s="24">
-        <f>Q11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="R13" s="24">
-        <f>R11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="S13" s="24">
-        <f>S11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="T13" s="24">
-        <f>T11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="U13" s="24">
-        <f>U11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="V13" s="24">
-        <f>V11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="C14" s="24">
-        <f>C12-C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>D12-D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="24">
-        <f>E12-E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="24">
-        <f>F12-F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="24">
-        <f>G12-G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="24">
-        <f>H12-H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="24">
-        <f>I12-I13</f>
-        <v/>
-      </c>
-      <c r="J14" s="24">
-        <f>J12-J13</f>
-        <v/>
-      </c>
-      <c r="K14" s="24">
-        <f>K12-K13</f>
-        <v/>
-      </c>
-      <c r="L14" s="24">
-        <f>L12-L13</f>
-        <v/>
-      </c>
-      <c r="M14" s="24">
-        <f>M12-M13</f>
-        <v/>
-      </c>
-      <c r="N14" s="24">
-        <f>N12-N13</f>
-        <v/>
-      </c>
-      <c r="O14" s="24">
-        <f>O12-O13</f>
-        <v/>
-      </c>
-      <c r="P14" s="24">
-        <f>P12-P13</f>
-        <v/>
-      </c>
-      <c r="Q14" s="24">
-        <f>Q12-Q13</f>
-        <v/>
-      </c>
-      <c r="R14" s="24">
-        <f>R12-R13</f>
-        <v/>
-      </c>
-      <c r="S14" s="24">
-        <f>S12-S13</f>
-        <v/>
-      </c>
-      <c r="T14" s="24">
-        <f>T12-T13</f>
-        <v/>
-      </c>
-      <c r="U14" s="24">
-        <f>U12-U13</f>
-        <v/>
-      </c>
-      <c r="V14" s="24">
-        <f>V12-V13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Ending balance</t>
-        </is>
-      </c>
-      <c r="C15" s="23">
-        <f>C11-C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="23">
-        <f>D11-D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="23">
-        <f>E11-E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="23">
-        <f>F11-F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="23">
-        <f>G11-G14</f>
-        <v/>
-      </c>
-      <c r="H15" s="23">
-        <f>H11-H14</f>
-        <v/>
-      </c>
-      <c r="I15" s="23">
-        <f>I11-I14</f>
-        <v/>
-      </c>
-      <c r="J15" s="23">
-        <f>J11-J14</f>
-        <v/>
-      </c>
-      <c r="K15" s="23">
-        <f>K11-K14</f>
-        <v/>
-      </c>
-      <c r="L15" s="23">
-        <f>L11-L14</f>
-        <v/>
-      </c>
-      <c r="M15" s="23">
-        <f>M11-M14</f>
-        <v/>
-      </c>
-      <c r="N15" s="23">
-        <f>N11-N14</f>
-        <v/>
-      </c>
-      <c r="O15" s="23">
-        <f>O11-O14</f>
-        <v/>
-      </c>
-      <c r="P15" s="23">
-        <f>P11-P14</f>
-        <v/>
-      </c>
-      <c r="Q15" s="23">
-        <f>Q11-Q14</f>
-        <v/>
-      </c>
-      <c r="R15" s="23">
-        <f>R11-R14</f>
-        <v/>
-      </c>
-      <c r="S15" s="23">
-        <f>S11-S14</f>
-        <v/>
-      </c>
-      <c r="T15" s="23">
-        <f>T11-T14</f>
-        <v/>
-      </c>
-      <c r="U15" s="23">
-        <f>U11-U14</f>
-        <v/>
-      </c>
-      <c r="V15" s="23">
-        <f>V11-V14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Beginning balance</t>
-        </is>
-      </c>
-      <c r="C18" s="25">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>C22</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>D22</f>
-        <v/>
-      </c>
-      <c r="F18" s="24">
-        <f>E22</f>
-        <v/>
-      </c>
-      <c r="G18" s="24">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H18" s="24">
-        <f>G22</f>
-        <v/>
-      </c>
-      <c r="I18" s="24">
-        <f>H22</f>
-        <v/>
-      </c>
-      <c r="J18" s="24">
-        <f>I22</f>
-        <v/>
-      </c>
-      <c r="K18" s="24">
-        <f>J22</f>
-        <v/>
-      </c>
-      <c r="L18" s="24">
-        <f>K22</f>
-        <v/>
-      </c>
-      <c r="M18" s="24">
-        <f>L22</f>
-        <v/>
-      </c>
-      <c r="N18" s="24">
-        <f>M22</f>
-        <v/>
-      </c>
-      <c r="O18" s="24">
-        <f>N22</f>
-        <v/>
-      </c>
-      <c r="P18" s="24">
-        <f>O22</f>
-        <v/>
-      </c>
-      <c r="Q18" s="24">
-        <f>P22</f>
-        <v/>
-      </c>
-      <c r="R18" s="24">
-        <f>Q22</f>
-        <v/>
-      </c>
-      <c r="S18" s="24">
-        <f>R22</f>
-        <v/>
-      </c>
-      <c r="T18" s="24">
-        <f>S22</f>
-        <v/>
-      </c>
-      <c r="U18" s="24">
-        <f>T22</f>
-        <v/>
-      </c>
-      <c r="V18" s="24">
-        <f>U22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ending balance (closed-form)</t>
-        </is>
-      </c>
-      <c r="C19" s="24">
-        <f>MAX(0,C18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>MAX(0,D18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>MAX(0,E18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
-        <f>MAX(0,F18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="G19" s="24">
-        <f>MAX(0,G18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="H19" s="24">
-        <f>MAX(0,H18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="I19" s="24">
-        <f>MAX(0,I18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="J19" s="24">
-        <f>MAX(0,J18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="K19" s="24">
-        <f>MAX(0,K18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="L19" s="24">
-        <f>MAX(0,L18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="M19" s="24">
-        <f>MAX(0,M18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="N19" s="24">
-        <f>MAX(0,N18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="O19" s="24">
-        <f>MAX(0,O18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="P19" s="24">
-        <f>MAX(0,P18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="24">
-        <f>MAX(0,Q18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="R19" s="24">
-        <f>MAX(0,R18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="S19" s="24">
-        <f>MAX(0,S18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="T19" s="24">
-        <f>MAX(0,T18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="U19" s="24">
-        <f>MAX(0,U18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="V19" s="24">
-        <f>MAX(0,V18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="C20" s="24">
-        <f>C18-C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>D18-D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="24">
-        <f>E18-E19</f>
-        <v/>
-      </c>
-      <c r="F20" s="24">
-        <f>F18-F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="24">
-        <f>G18-G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="24">
-        <f>H18-H19</f>
-        <v/>
-      </c>
-      <c r="I20" s="24">
-        <f>I18-I19</f>
-        <v/>
-      </c>
-      <c r="J20" s="24">
-        <f>J18-J19</f>
-        <v/>
-      </c>
-      <c r="K20" s="24">
-        <f>K18-K19</f>
-        <v/>
-      </c>
-      <c r="L20" s="24">
-        <f>L18-L19</f>
-        <v/>
-      </c>
-      <c r="M20" s="24">
-        <f>M18-M19</f>
-        <v/>
-      </c>
-      <c r="N20" s="24">
-        <f>N18-N19</f>
-        <v/>
-      </c>
-      <c r="O20" s="24">
-        <f>O18-O19</f>
-        <v/>
-      </c>
-      <c r="P20" s="24">
-        <f>P18-P19</f>
-        <v/>
-      </c>
-      <c r="Q20" s="24">
-        <f>Q18-Q19</f>
-        <v/>
-      </c>
-      <c r="R20" s="24">
-        <f>R18-R19</f>
-        <v/>
-      </c>
-      <c r="S20" s="24">
-        <f>S18-S19</f>
-        <v/>
-      </c>
-      <c r="T20" s="24">
-        <f>T18-T19</f>
-        <v/>
-      </c>
-      <c r="U20" s="24">
-        <f>U18-U19</f>
-        <v/>
-      </c>
-      <c r="V20" s="24">
-        <f>V18-V19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="C21" s="24">
-        <f>MAX(0,IF(C18=0,0,'Debt Schedule'!$B$6*1-C20))</f>
-        <v/>
-      </c>
-      <c r="D21" s="24">
-        <f>MAX(0,IF(D18=0,0,'Debt Schedule'!$B$6*1-D20))</f>
-        <v/>
-      </c>
-      <c r="E21" s="24">
-        <f>MAX(0,IF(E18=0,0,'Debt Schedule'!$B$6*1-E20))</f>
-        <v/>
-      </c>
-      <c r="F21" s="24">
-        <f>MAX(0,IF(F18=0,0,'Debt Schedule'!$B$6*1-F20))</f>
-        <v/>
-      </c>
-      <c r="G21" s="24">
-        <f>MAX(0,IF(G18=0,0,'Debt Schedule'!$B$6*1-G20))</f>
-        <v/>
-      </c>
-      <c r="H21" s="24">
-        <f>MAX(0,IF(H18=0,0,'Debt Schedule'!$B$6*1-H20))</f>
-        <v/>
-      </c>
-      <c r="I21" s="24">
-        <f>MAX(0,IF(I18=0,0,'Debt Schedule'!$B$6*1-I20))</f>
-        <v/>
-      </c>
-      <c r="J21" s="24">
-        <f>MAX(0,IF(J18=0,0,'Debt Schedule'!$B$6*1-J20))</f>
-        <v/>
-      </c>
-      <c r="K21" s="24">
-        <f>MAX(0,IF(K18=0,0,'Debt Schedule'!$B$6*1-K20))</f>
-        <v/>
-      </c>
-      <c r="L21" s="24">
-        <f>MAX(0,IF(L18=0,0,'Debt Schedule'!$B$6*1-L20))</f>
-        <v/>
-      </c>
-      <c r="M21" s="24">
-        <f>MAX(0,IF(M18=0,0,'Debt Schedule'!$B$6*1-M20))</f>
-        <v/>
-      </c>
-      <c r="N21" s="24">
-        <f>MAX(0,IF(N18=0,0,'Debt Schedule'!$B$6*1-N20))</f>
-        <v/>
-      </c>
-      <c r="O21" s="24">
-        <f>MAX(0,IF(O18=0,0,'Debt Schedule'!$B$6*3-O20))</f>
-        <v/>
-      </c>
-      <c r="P21" s="24">
-        <f>MAX(0,IF(P18=0,0,'Debt Schedule'!$B$6*3-P20))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="24">
-        <f>MAX(0,IF(Q18=0,0,'Debt Schedule'!$B$6*3-Q20))</f>
-        <v/>
-      </c>
-      <c r="R21" s="24">
-        <f>MAX(0,IF(R18=0,0,'Debt Schedule'!$B$6*3-R20))</f>
-        <v/>
-      </c>
-      <c r="S21" s="24">
-        <f>MAX(0,IF(S18=0,0,'Debt Schedule'!$B$6*3-S20))</f>
-        <v/>
-      </c>
-      <c r="T21" s="24">
-        <f>MAX(0,IF(T18=0,0,'Debt Schedule'!$B$6*3-T20))</f>
-        <v/>
-      </c>
-      <c r="U21" s="24">
-        <f>MAX(0,IF(U18=0,0,'Debt Schedule'!$B$6*3-U20))</f>
-        <v/>
-      </c>
-      <c r="V21" s="24">
-        <f>MAX(0,IF(V18=0,0,'Debt Schedule'!$B$6*3-V20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>Ending balance</t>
-        </is>
-      </c>
-      <c r="C22" s="23">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="D22" s="23">
-        <f>D19</f>
-        <v/>
-      </c>
-      <c r="E22" s="23">
-        <f>E19</f>
-        <v/>
-      </c>
-      <c r="F22" s="23">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="G22" s="23">
-        <f>G19</f>
-        <v/>
-      </c>
-      <c r="H22" s="23">
-        <f>H19</f>
-        <v/>
-      </c>
-      <c r="I22" s="23">
-        <f>I19</f>
-        <v/>
-      </c>
-      <c r="J22" s="23">
-        <f>J19</f>
-        <v/>
-      </c>
-      <c r="K22" s="23">
-        <f>K19</f>
-        <v/>
-      </c>
-      <c r="L22" s="23">
-        <f>L19</f>
-        <v/>
-      </c>
-      <c r="M22" s="23">
-        <f>M19</f>
-        <v/>
-      </c>
-      <c r="N22" s="23">
-        <f>N19</f>
-        <v/>
-      </c>
-      <c r="O22" s="23">
-        <f>O19</f>
-        <v/>
-      </c>
-      <c r="P22" s="23">
-        <f>P19</f>
-        <v/>
-      </c>
-      <c r="Q22" s="23">
-        <f>Q19</f>
-        <v/>
-      </c>
-      <c r="R22" s="23">
-        <f>R19</f>
-        <v/>
-      </c>
-      <c r="S22" s="23">
-        <f>S19</f>
-        <v/>
-      </c>
-      <c r="T22" s="23">
-        <f>T19</f>
-        <v/>
-      </c>
-      <c r="U22" s="23">
-        <f>U19</f>
-        <v/>
-      </c>
-      <c r="V22" s="23">
-        <f>V19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Total interest</t>
-        </is>
-      </c>
-      <c r="C25" s="24">
-        <f>C13+C21</f>
-        <v/>
-      </c>
-      <c r="D25" s="24">
-        <f>D13+D21</f>
-        <v/>
-      </c>
-      <c r="E25" s="24">
-        <f>E13+E21</f>
-        <v/>
-      </c>
-      <c r="F25" s="24">
-        <f>F13+F21</f>
-        <v/>
-      </c>
-      <c r="G25" s="24">
-        <f>G13+G21</f>
-        <v/>
-      </c>
-      <c r="H25" s="24">
-        <f>H13+H21</f>
-        <v/>
-      </c>
-      <c r="I25" s="24">
-        <f>I13+I21</f>
-        <v/>
-      </c>
-      <c r="J25" s="24">
-        <f>J13+J21</f>
-        <v/>
-      </c>
-      <c r="K25" s="24">
-        <f>K13+K21</f>
-        <v/>
-      </c>
-      <c r="L25" s="24">
-        <f>L13+L21</f>
-        <v/>
-      </c>
-      <c r="M25" s="24">
-        <f>M13+M21</f>
-        <v/>
-      </c>
-      <c r="N25" s="24">
-        <f>N13+N21</f>
-        <v/>
-      </c>
-      <c r="O25" s="24">
-        <f>O13+O21</f>
-        <v/>
-      </c>
-      <c r="P25" s="24">
-        <f>P13+P21</f>
-        <v/>
-      </c>
-      <c r="Q25" s="24">
-        <f>Q13+Q21</f>
-        <v/>
-      </c>
-      <c r="R25" s="24">
-        <f>R13+R21</f>
-        <v/>
-      </c>
-      <c r="S25" s="24">
-        <f>S13+S21</f>
-        <v/>
-      </c>
-      <c r="T25" s="24">
-        <f>T13+T21</f>
-        <v/>
-      </c>
-      <c r="U25" s="24">
-        <f>U13+U21</f>
-        <v/>
-      </c>
-      <c r="V25" s="24">
-        <f>V13+V21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Total principal</t>
-        </is>
-      </c>
-      <c r="C26" s="24">
-        <f>C14+C20</f>
-        <v/>
-      </c>
-      <c r="D26" s="24">
-        <f>D14+D20</f>
-        <v/>
-      </c>
-      <c r="E26" s="24">
-        <f>E14+E20</f>
-        <v/>
-      </c>
-      <c r="F26" s="24">
-        <f>F14+F20</f>
-        <v/>
-      </c>
-      <c r="G26" s="24">
-        <f>G14+G20</f>
-        <v/>
-      </c>
-      <c r="H26" s="24">
-        <f>H14+H20</f>
-        <v/>
-      </c>
-      <c r="I26" s="24">
-        <f>I14+I20</f>
-        <v/>
-      </c>
-      <c r="J26" s="24">
-        <f>J14+J20</f>
-        <v/>
-      </c>
-      <c r="K26" s="24">
-        <f>K14+K20</f>
-        <v/>
-      </c>
-      <c r="L26" s="24">
-        <f>L14+L20</f>
-        <v/>
-      </c>
-      <c r="M26" s="24">
-        <f>M14+M20</f>
-        <v/>
-      </c>
-      <c r="N26" s="24">
-        <f>N14+N20</f>
-        <v/>
-      </c>
-      <c r="O26" s="24">
-        <f>O14+O20</f>
-        <v/>
-      </c>
-      <c r="P26" s="24">
-        <f>P14+P20</f>
-        <v/>
-      </c>
-      <c r="Q26" s="24">
-        <f>Q14+Q20</f>
-        <v/>
-      </c>
-      <c r="R26" s="24">
-        <f>R14+R20</f>
-        <v/>
-      </c>
-      <c r="S26" s="24">
-        <f>S14+S20</f>
-        <v/>
-      </c>
-      <c r="T26" s="24">
-        <f>T14+T20</f>
-        <v/>
-      </c>
-      <c r="U26" s="24">
-        <f>U14+U20</f>
-        <v/>
-      </c>
-      <c r="V26" s="24">
-        <f>V14+V20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL DEBT SERVICE (P+I)</t>
-        </is>
-      </c>
-      <c r="C27" s="23">
-        <f>C25+C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="23">
-        <f>D25+D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="23">
-        <f>E25+E26</f>
-        <v/>
-      </c>
-      <c r="F27" s="23">
-        <f>F25+F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="23">
-        <f>G25+G26</f>
-        <v/>
-      </c>
-      <c r="H27" s="23">
-        <f>H25+H26</f>
-        <v/>
-      </c>
-      <c r="I27" s="23">
-        <f>I25+I26</f>
-        <v/>
-      </c>
-      <c r="J27" s="23">
-        <f>J25+J26</f>
-        <v/>
-      </c>
-      <c r="K27" s="23">
-        <f>K25+K26</f>
-        <v/>
-      </c>
-      <c r="L27" s="23">
-        <f>L25+L26</f>
-        <v/>
-      </c>
-      <c r="M27" s="23">
-        <f>M25+M26</f>
-        <v/>
-      </c>
-      <c r="N27" s="23">
-        <f>N25+N26</f>
-        <v/>
-      </c>
-      <c r="O27" s="23">
-        <f>O25+O26</f>
-        <v/>
-      </c>
-      <c r="P27" s="23">
-        <f>P25+P26</f>
-        <v/>
-      </c>
-      <c r="Q27" s="23">
-        <f>Q25+Q26</f>
-        <v/>
-      </c>
-      <c r="R27" s="23">
-        <f>R25+R26</f>
-        <v/>
-      </c>
-      <c r="S27" s="23">
-        <f>S25+S26</f>
-        <v/>
-      </c>
-      <c r="T27" s="23">
-        <f>T25+T26</f>
-        <v/>
-      </c>
-      <c r="U27" s="23">
-        <f>U25+U26</f>
-        <v/>
-      </c>
-      <c r="V27" s="23">
-        <f>V25+V26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>EBITDA (link)</t>
-        </is>
-      </c>
-      <c r="C28" s="25">
-        <f>'Operating Budget'!C24</f>
-        <v/>
-      </c>
-      <c r="D28" s="25">
-        <f>'Operating Budget'!D24</f>
-        <v/>
-      </c>
-      <c r="E28" s="25">
-        <f>'Operating Budget'!E24</f>
-        <v/>
-      </c>
-      <c r="F28" s="25">
-        <f>'Operating Budget'!F24</f>
-        <v/>
-      </c>
-      <c r="G28" s="25">
-        <f>'Operating Budget'!G24</f>
-        <v/>
-      </c>
-      <c r="H28" s="25">
-        <f>'Operating Budget'!H24</f>
-        <v/>
-      </c>
-      <c r="I28" s="25">
-        <f>'Operating Budget'!I24</f>
-        <v/>
-      </c>
-      <c r="J28" s="25">
-        <f>'Operating Budget'!J24</f>
-        <v/>
-      </c>
-      <c r="K28" s="25">
-        <f>'Operating Budget'!K24</f>
-        <v/>
-      </c>
-      <c r="L28" s="25">
-        <f>'Operating Budget'!L24</f>
-        <v/>
-      </c>
-      <c r="M28" s="25">
-        <f>'Operating Budget'!M24</f>
-        <v/>
-      </c>
-      <c r="N28" s="25">
-        <f>'Operating Budget'!N24</f>
-        <v/>
-      </c>
-      <c r="O28" s="25">
-        <f>'Operating Budget'!O24</f>
-        <v/>
-      </c>
-      <c r="P28" s="25">
-        <f>'Operating Budget'!P24</f>
-        <v/>
-      </c>
-      <c r="Q28" s="25">
-        <f>'Operating Budget'!Q24</f>
-        <v/>
-      </c>
-      <c r="R28" s="25">
-        <f>'Operating Budget'!R24</f>
-        <v/>
-      </c>
-      <c r="S28" s="25">
-        <f>'Operating Budget'!S24</f>
-        <v/>
-      </c>
-      <c r="T28" s="25">
-        <f>'Operating Budget'!T24</f>
-        <v/>
-      </c>
-      <c r="U28" s="25">
-        <f>'Operating Budget'!U24</f>
-        <v/>
-      </c>
-      <c r="V28" s="25">
-        <f>'Operating Budget'!V24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>DSCR (period)</t>
-        </is>
-      </c>
-      <c r="C29" s="57">
-        <f>IF(C27=0,0,C28/C27)</f>
-        <v/>
-      </c>
-      <c r="D29" s="57">
-        <f>IF(D27=0,0,D28/D27)</f>
-        <v/>
-      </c>
-      <c r="E29" s="57">
-        <f>IF(E27=0,0,E28/E27)</f>
-        <v/>
-      </c>
-      <c r="F29" s="57">
-        <f>IF(F27=0,0,F28/F27)</f>
-        <v/>
-      </c>
-      <c r="G29" s="57">
-        <f>IF(G27=0,0,G28/G27)</f>
-        <v/>
-      </c>
-      <c r="H29" s="57">
-        <f>IF(H27=0,0,H28/H27)</f>
-        <v/>
-      </c>
-      <c r="I29" s="57">
-        <f>IF(I27=0,0,I28/I27)</f>
-        <v/>
-      </c>
-      <c r="J29" s="57">
-        <f>IF(J27=0,0,J28/J27)</f>
-        <v/>
-      </c>
-      <c r="K29" s="57">
-        <f>IF(K27=0,0,K28/K27)</f>
-        <v/>
-      </c>
-      <c r="L29" s="57">
-        <f>IF(L27=0,0,L28/L27)</f>
-        <v/>
-      </c>
-      <c r="M29" s="57">
-        <f>IF(M27=0,0,M28/M27)</f>
-        <v/>
-      </c>
-      <c r="N29" s="57">
-        <f>IF(N27=0,0,N28/N27)</f>
-        <v/>
-      </c>
-      <c r="O29" s="57">
-        <f>IF(O27=0,0,O28/O27)</f>
-        <v/>
-      </c>
-      <c r="P29" s="57">
-        <f>IF(P27=0,0,P28/P27)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="57">
-        <f>IF(Q27=0,0,Q28/Q27)</f>
-        <v/>
-      </c>
-      <c r="R29" s="57">
-        <f>IF(R27=0,0,R28/R27)</f>
-        <v/>
-      </c>
-      <c r="S29" s="57">
-        <f>IF(S27=0,0,S28/S27)</f>
-        <v/>
-      </c>
-      <c r="T29" s="57">
-        <f>IF(T27=0,0,T28/T27)</f>
-        <v/>
-      </c>
-      <c r="U29" s="57">
-        <f>IF(U27=0,0,U28/U27)</f>
-        <v/>
-      </c>
-      <c r="V29" s="57">
-        <f>IF(V27=0,0,V28/V27)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A10:V10"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="A17:V17"/>
-    <mergeCell ref="C8:N8"/>
-    <mergeCell ref="A4:V4"/>
-    <mergeCell ref="A24:V24"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/financial_models/output/Azalea_Hospice_SBA_Loan_Package.xlsx
+++ b/financial_models/output/Azalea_Hospice_SBA_Loan_Package.xlsx
@@ -1210,22 +1210,22 @@
     </comment>
     <comment ref="B110" authorId="0" shapeId="0">
       <text>
-        <t>Sized to pay the seller in full at close + fund startup costs and working-capital reserve. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Sized for startup costs + working-capital reserve (the Hickory acquisition is funded by the bank term loan below). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0" shapeId="0">
       <text>
-        <t>FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Typical 7(a) variable: Prime ~7.5% + 3.0% spread. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B112" authorId="0" shapeId="0">
       <text>
-        <t>10-year amortization. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>15-year amortization. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B113" authorId="0" shapeId="0">
       <text>
-        <t>Cash capital contribution by James Bullard (19.5% passive member). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Cash capital contribution by James Bullard (19.5% passive member); $180K designated as the SBA equity injection. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B114" authorId="0" shapeId="0">
@@ -1260,22 +1260,22 @@
     </comment>
     <comment ref="B120" authorId="0" shapeId="0">
       <text>
-        <t>CHOW: acquire Hickory Hospice's existing Medicare-certified provider number (San Antonio + Tyler alternative-delivery site). Eliminates 855A enrollment gap - Azalea bills from day 1.</t>
+        <t>CHOW: purchase 100% of Hickory Hospice LLC's membership interests; its Medicare-certified provider number conveys with the entity (Azalea bills from day 1). Funded by the bank term loan below.</t>
       </text>
     </comment>
     <comment ref="B121" authorId="0" shapeId="0">
       <text>
-        <t>Seller financing on the license acquisition.</t>
+        <t>Concurrent bank term loan (Jim Bullard's bank); Jim personally guarantees. Subordinate to the SBA loan.</t>
       </text>
     </comment>
     <comment ref="B122" authorId="0" shapeId="0">
       <text>
-        <t>Monthly P+I amortization.</t>
+        <t>3-year monthly P+I amortization.</t>
       </text>
     </comment>
     <comment ref="B123" authorId="0" shapeId="0">
       <text>
-        <t>GAAP intangible amortization - non-cash, below EBITDA. No effect on DSCR.</t>
+        <t>GAAP intangible amortization - non-cash, below EBITDA. No effect on DSCR. Confirm tax treatment of a membership-interest purchase with CPA.</t>
       </text>
     </comment>
     <comment ref="B126" authorId="0" shapeId="0">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B110" s="9" t="n">
-        <v>555000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="111">
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="B111" s="7" t="n">
-        <v>0.115</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="112">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="B112" s="17" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="113">
@@ -3500,7 +3500,7 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Hickory Medicare license - acquisition cost ($)</t>
+          <t>Hickory acquisition - purchase price ($)</t>
         </is>
       </c>
       <c r="B120" s="9" t="n">
@@ -3510,7 +3510,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>License note interest rate (APR)</t>
+          <t>Acquisition bank loan rate (APR)</t>
         </is>
       </c>
       <c r="B121" s="7" t="n">
@@ -3520,7 +3520,7 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>License note term (months)</t>
+          <t>Acquisition bank loan term (months)</t>
         </is>
       </c>
       <c r="B122" s="17" t="n">
@@ -3530,7 +3530,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>License intangible amortization life (yrs)</t>
+          <t>Acquisition intangible amortization life (yrs)</t>
         </is>
       </c>
       <c r="B123" s="17" t="n">
@@ -3652,11 +3652,11 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>Opening cash = equity + loan - startup - capex - license (paid at close)</t>
+          <t>Opening cash = equity + loan - startup - capex</t>
         </is>
       </c>
       <c r="B139" s="23">
-        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117-Inputs!$B$120</f>
+        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117</f>
         <v/>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
+          <t>Debt Schedule - SBA 7(a) + Hickory license seller note | Combined DSCR shown (target &gt;= 1.25x)</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>0</f>
+        <f>PMT(Inputs!$B$121/12,Inputs!$B$122,-Inputs!$B$120)</f>
         <v/>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
+          <t>HICKORY LICENSE SELLER NOTE ($300K, 6%, 36 mo)</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="C18" s="25">
-        <f>0</f>
+        <f>Inputs!$B$120</f>
         <v/>
       </c>
       <c r="D18" s="24">
@@ -4786,7 +4786,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
+          <t>COMBINED DEBT SERVICE &amp; COVERAGE</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4967,7 @@
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>TOTAL DEBT SERVICE (P+I)</t>
+          <t>TOTAL DEBT SERVICE (P+I, combined)</t>
         </is>
       </c>
       <c r="C27" s="23">
@@ -5141,7 +5141,7 @@
     <row r="29">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>DSCR (period)</t>
+          <t>COMBINED DSCR (period)</t>
         </is>
       </c>
       <c r="C29" s="57">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="B34" s="25">
-        <f>0</f>
+        <f>Inputs!$B$120</f>
         <v/>
       </c>
       <c r="C34" s="25">
@@ -8501,7 +8501,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sources &amp; Uses of Financing - Hickory CHOW (seller paid at close) + working capital | SBA + equity</t>
+          <t>Sources &amp; Uses of Financing - Hickory CHOW acquisition + working capital | SBA + seller note + equity</t>
         </is>
       </c>
     </row>
@@ -8540,11 +8540,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Owner equity injection</t>
+          <t>Hickory license seller note</t>
         </is>
       </c>
       <c r="B6" s="25">
-        <f>Inputs!$B$113</f>
+        <f>Inputs!$B$120</f>
         <v/>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -8558,13 +8558,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL SOURCES</t>
-        </is>
-      </c>
-      <c r="B7" s="27">
-        <f>SUM(B5:B6)</f>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Owner equity injection</t>
+        </is>
+      </c>
+      <c r="B7" s="25">
+        <f>Inputs!$B$113</f>
         <v/>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -8578,6 +8578,15 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL SOURCES</t>
+        </is>
+      </c>
+      <c r="B8" s="27">
+        <f>SUM(B5:B7)</f>
+        <v/>
+      </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>EMR implementation / setup</t>
@@ -8661,14 +8670,14 @@
         </is>
       </c>
       <c r="B16" s="28">
-        <f>B7-D14</f>
+        <f>B8-D14</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>CHOW acquisition: Azalea acquires Hickory Hospice's existing Medicare-certified provider number ($300K, paid in full at close from SBA loan + equity proceeds) - gives Azalea immediate billing capability in San Antonio and an alternative-delivery site serving the East Texas / Tyler market. CHAP/ACHC accreditation transfers with the CHOW; 855A change-of-ownership preserves the provider number with no fresh enrollment delay. With no seller note, the SBA loan is the only debt the business carries.</t>
+          <t>CHOW acquisition: Azalea acquires Hickory Hospice's existing Medicare-certified provider number ($300K, 36 months at 6% seller-financed) - gives Azalea immediate billing capability in San Antonio and an alternative-delivery site serving the East Texas / Tyler market. CHAP/ACHC accreditation transfers with the CHOW; 855A change-of-ownership preserves the provider number with no fresh enrollment delay. The seller note self-finances the license - it shows on both sides above.</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8722,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lender Summary - SBA 7(a) debt-service coverage (seller paid at close) vs SBA floor 1.25x</t>
+          <t>Lender Summary - COMBINED debt-service coverage (SBA + Hickory seller note) vs SBA floor 1.25x</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8930,7 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Azalea acquires Hickory Hospice's already-certified Medicare provider number via a $300K CHOW (paid in full at close), eliminating the 855A enrollment cash gap a fresh startup would face - Azalea bills from day 1 in San Antonio and operates an alternative-delivery site for Tyler/East Texas. The migrated Paloma clinical team brings a proven ~$118K/mo, ~22 ADC book of business. With the seller paid at close, the SBA loan is the only debt the business carries, so the coverage shown here is SBA-only - strong from Year 1.</t>
+          <t>Azalea acquires Hickory Hospice's already-certified Medicare provider number via a $300K CHOW (seller-financed at 6% over 36 months), eliminating the 855A enrollment cash gap a fresh startup would face - Azalea bills from day 1 in San Antonio and operates an alternative-delivery site for Tyler/East Texas. The migrated Paloma clinical team brings a proven ~$118K/mo, ~22 ADC book of business. Coverage shown here is COMBINED (SBA + seller note); the seller note retires at month 36, after which DSCR jumps as only the SBA service remains.</t>
         </is>
       </c>
     </row>
